--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2015/American_Aircraft_Cumulative_Statistics_2015.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2015/American_Aircraft_Cumulative_Statistics_2015.xlsx
@@ -13,33 +13,48 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="26" uniqueCount="26">
   <si>
     <t>Row</t>
   </si>
   <si>
-    <t>Allegiant</t>
-  </si>
-  <si>
-    <t>American</t>
-  </si>
-  <si>
-    <t>Delta</t>
-  </si>
-  <si>
-    <t>Frontier</t>
-  </si>
-  <si>
-    <t>JetBlue</t>
-  </si>
-  <si>
-    <t>Spirit</t>
-  </si>
-  <si>
-    <t>United</t>
-  </si>
-  <si>
-    <t>All Airlines</t>
+    <t>E190</t>
+  </si>
+  <si>
+    <t>A319</t>
+  </si>
+  <si>
+    <t>A320</t>
+  </si>
+  <si>
+    <t>A321</t>
+  </si>
+  <si>
+    <t>B737-800</t>
+  </si>
+  <si>
+    <t>B757-200</t>
+  </si>
+  <si>
+    <t>B767-300</t>
+  </si>
+  <si>
+    <t>A330-200</t>
+  </si>
+  <si>
+    <t>A330-300</t>
+  </si>
+  <si>
+    <t>B787-8</t>
+  </si>
+  <si>
+    <t>B777-200</t>
+  </si>
+  <si>
+    <t>B777-300</t>
+  </si>
+  <si>
+    <t>All Aircraft</t>
   </si>
   <si>
     <t>RPMs</t>
@@ -121,10 +136,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.5703125" customWidth="true"/>
+    <col min="1" max="1" width="9.140625" customWidth="true"/>
     <col min="2" max="2" width="15.85546875" customWidth="true"/>
     <col min="3" max="3" width="15.85546875" customWidth="true"/>
     <col min="4" max="4" width="13.140625" customWidth="true"/>
@@ -144,40 +159,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2">
@@ -185,40 +200,40 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>1760049676</v>
+        <v>566326667</v>
       </c>
       <c r="C2" s="0">
-        <v>2100846369</v>
+        <v>720129573</v>
       </c>
       <c r="D2" s="0">
-        <v>707356</v>
+        <v>195687</v>
       </c>
       <c r="E2" s="0">
-        <v>177</v>
+        <v>99</v>
       </c>
       <c r="F2" s="0">
-        <v>13073</v>
+        <v>18285</v>
       </c>
       <c r="G2" s="0">
-        <v>4.4000000000000004</v>
+        <v>4.9699999999999998</v>
       </c>
       <c r="H2" s="0">
-        <v>10.460000000000001</v>
+        <v>7.9400000000000004</v>
       </c>
       <c r="I2" s="0">
-        <v>83.780000000000001</v>
+        <v>78.640000000000001</v>
       </c>
       <c r="J2" s="0">
-        <v>907</v>
+        <v>398</v>
       </c>
       <c r="K2" s="0">
-        <v>2939</v>
+        <v>1878.49</v>
       </c>
       <c r="L2" s="0">
-        <v>16.59</v>
+        <v>18.98</v>
       </c>
       <c r="M2" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.075999999999999998</v>
       </c>
     </row>
     <row r="3">
@@ -226,40 +241,40 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>4560811144</v>
+        <v>9428197392</v>
       </c>
       <c r="C3" s="0">
-        <v>5270294262</v>
+        <v>11572465881</v>
       </c>
       <c r="D3" s="0">
-        <v>514175</v>
+        <v>408632</v>
       </c>
       <c r="E3" s="0">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="F3" s="0">
-        <v>36923</v>
+        <v>110511</v>
       </c>
       <c r="G3" s="0">
-        <v>3.6000000000000001</v>
+        <v>3.8999999999999999</v>
       </c>
       <c r="H3" s="0">
-        <v>9.2599999999999998</v>
+        <v>9.1400000000000006</v>
       </c>
       <c r="I3" s="0">
-        <v>86.540000000000006</v>
+        <v>81.469999999999999</v>
       </c>
       <c r="J3" s="0">
-        <v>952</v>
+        <v>833</v>
       </c>
       <c r="K3" s="0">
-        <v>3375</v>
+        <v>2929.48</v>
       </c>
       <c r="L3" s="0">
-        <v>22.5</v>
+        <v>23.329999999999998</v>
       </c>
       <c r="M3" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.066000000000000003</v>
       </c>
     </row>
     <row r="4">
@@ -267,40 +282,40 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>11629424764</v>
+        <v>4560811144</v>
       </c>
       <c r="C4" s="0">
-        <v>13544742291</v>
+        <v>5270294262</v>
       </c>
       <c r="D4" s="0">
-        <v>544841</v>
+        <v>514175</v>
       </c>
       <c r="E4" s="0">
         <v>150</v>
       </c>
       <c r="F4" s="0">
-        <v>97564</v>
+        <v>36923</v>
       </c>
       <c r="G4" s="0">
-        <v>3.9199999999999999</v>
+        <v>3.6000000000000001</v>
       </c>
       <c r="H4" s="0">
-        <v>9.6799999999999997</v>
+        <v>9.2599999999999998</v>
       </c>
       <c r="I4" s="0">
-        <v>85.859999999999999</v>
+        <v>86.540000000000006</v>
       </c>
       <c r="J4" s="0">
-        <v>924</v>
+        <v>952</v>
       </c>
       <c r="K4" s="0">
-        <v>3982</v>
+        <v>3374.7199999999998</v>
       </c>
       <c r="L4" s="0">
-        <v>26.489999999999998</v>
+        <v>22.5</v>
       </c>
       <c r="M4" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.060999999999999999</v>
       </c>
     </row>
     <row r="5">
@@ -308,37 +323,37 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>5935492797</v>
+        <v>23158589443</v>
       </c>
       <c r="C5" s="0">
-        <v>6897657906</v>
+        <v>26416735977</v>
       </c>
       <c r="D5" s="0">
-        <v>861131</v>
+        <v>711466</v>
       </c>
       <c r="E5" s="0">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F5" s="0">
-        <v>34266</v>
+        <v>120282</v>
       </c>
       <c r="G5" s="0">
-        <v>4.2800000000000002</v>
+        <v>3.2400000000000002</v>
       </c>
       <c r="H5" s="0">
-        <v>12.6</v>
+        <v>10.640000000000001</v>
       </c>
       <c r="I5" s="0">
-        <v>86.049999999999997</v>
+        <v>87.670000000000002</v>
       </c>
       <c r="J5" s="0">
-        <v>1141</v>
+        <v>1292</v>
       </c>
       <c r="K5" s="0">
-        <v>4027</v>
+        <v>4004.48</v>
       </c>
       <c r="L5" s="0">
-        <v>22.829999999999998</v>
+        <v>23.379999999999999</v>
       </c>
       <c r="M5" s="0">
         <v>0.059999999999999998</v>
@@ -349,40 +364,40 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>30737665585</v>
+        <v>50327245616</v>
       </c>
       <c r="C6" s="0">
-        <v>36235086450</v>
+        <v>59161129896</v>
       </c>
       <c r="D6" s="0">
-        <v>763487</v>
+        <v>630985</v>
       </c>
       <c r="E6" s="0">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="F6" s="0">
-        <v>184660</v>
+        <v>321353</v>
       </c>
       <c r="G6" s="0">
-        <v>3.8900000000000001</v>
+        <v>3.4300000000000002</v>
       </c>
       <c r="H6" s="0">
-        <v>12.69</v>
+        <v>10.390000000000001</v>
       </c>
       <c r="I6" s="0">
-        <v>84.829999999999998</v>
+        <v>85.069999999999993</v>
       </c>
       <c r="J6" s="0">
-        <v>1308</v>
+        <v>1160</v>
       </c>
       <c r="K6" s="0">
-        <v>3567</v>
+        <v>3723.4699999999998</v>
       </c>
       <c r="L6" s="0">
-        <v>23.780000000000001</v>
+        <v>23.449999999999999</v>
       </c>
       <c r="M6" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.060999999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -390,40 +405,40 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>11002080040</v>
+        <v>14253643738</v>
       </c>
       <c r="C7" s="0">
-        <v>13073955850</v>
+        <v>17251123975</v>
       </c>
       <c r="D7" s="0">
-        <v>858434</v>
+        <v>671773</v>
       </c>
       <c r="E7" s="0">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F7" s="0">
-        <v>73711</v>
+        <v>55827</v>
       </c>
       <c r="G7" s="0">
-        <v>4.8399999999999999</v>
+        <v>2.1699999999999999</v>
       </c>
       <c r="H7" s="0">
-        <v>12.69</v>
+        <v>8.8499999999999996</v>
       </c>
       <c r="I7" s="0">
-        <v>84.150000000000006</v>
+        <v>82.620000000000005</v>
       </c>
       <c r="J7" s="0">
-        <v>994</v>
+        <v>1725</v>
       </c>
       <c r="K7" s="0">
-        <v>3135</v>
+        <v>4899.79</v>
       </c>
       <c r="L7" s="0">
-        <v>17.579999999999998</v>
+        <v>27.32</v>
       </c>
       <c r="M7" s="0">
-        <v>0.050000000000000003</v>
+        <v>0.065000000000000002</v>
       </c>
     </row>
     <row r="8">
@@ -431,40 +446,40 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>16757952628</v>
+        <v>14098042796</v>
       </c>
       <c r="C8" s="0">
-        <v>19422625200</v>
+        <v>17913364784</v>
       </c>
       <c r="D8" s="0">
-        <v>548352</v>
+        <v>900622</v>
       </c>
       <c r="E8" s="0">
-        <v>150</v>
+        <v>211</v>
       </c>
       <c r="F8" s="0">
-        <v>119746</v>
+        <v>28687</v>
       </c>
       <c r="G8" s="0">
-        <v>3.3799999999999999</v>
+        <v>1.4399999999999999</v>
       </c>
       <c r="H8" s="0">
-        <v>9.5</v>
+        <v>9.3200000000000003</v>
       </c>
       <c r="I8" s="0">
-        <v>86.280000000000001</v>
+        <v>78.700000000000003</v>
       </c>
       <c r="J8" s="0">
-        <v>1081</v>
+        <v>2980</v>
       </c>
       <c r="K8" s="0">
-        <v>3810</v>
+        <v>6470.4200000000001</v>
       </c>
       <c r="L8" s="0">
-        <v>25.399999999999999</v>
+        <v>30.859999999999999</v>
       </c>
       <c r="M8" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.067000000000000004</v>
       </c>
     </row>
     <row r="9">
@@ -472,40 +487,245 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>82383476634</v>
+        <v>3296354852</v>
       </c>
       <c r="C9" s="0">
-        <v>96545208328</v>
+        <v>4228269219</v>
       </c>
       <c r="D9" s="0">
-        <v>669523</v>
+        <v>1526451</v>
       </c>
       <c r="E9" s="0">
-        <v>156</v>
+        <v>254</v>
       </c>
       <c r="F9" s="0">
-        <v>559943</v>
+        <v>4624</v>
       </c>
       <c r="G9" s="0">
-        <v>3.8799999999999999</v>
+        <v>1.6699999999999999</v>
       </c>
       <c r="H9" s="0">
-        <v>11.09</v>
+        <v>12.76</v>
       </c>
       <c r="I9" s="0">
-        <v>85.329999999999998</v>
+        <v>77.959999999999994</v>
       </c>
       <c r="J9" s="0">
-        <v>1108</v>
+        <v>3611</v>
       </c>
       <c r="K9" s="0">
-        <v>3634</v>
+        <v>7221.1800000000003</v>
       </c>
       <c r="L9" s="0">
-        <v>23.34</v>
+        <v>28.510000000000002</v>
       </c>
       <c r="M9" s="0">
         <v>0.059999999999999998</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="0">
+        <v>2205260037</v>
+      </c>
+      <c r="C10" s="0">
+        <v>2832108740</v>
+      </c>
+      <c r="D10" s="0">
+        <v>1706090</v>
+      </c>
+      <c r="E10" s="0">
+        <v>287</v>
+      </c>
+      <c r="F10" s="0">
+        <v>2900</v>
+      </c>
+      <c r="G10" s="0">
+        <v>1.75</v>
+      </c>
+      <c r="H10" s="0">
+        <v>12.81</v>
+      </c>
+      <c r="I10" s="0">
+        <v>77.870000000000005</v>
+      </c>
+      <c r="J10" s="0">
+        <v>3412</v>
+      </c>
+      <c r="K10" s="0">
+        <v>7980.4899999999998</v>
+      </c>
+      <c r="L10" s="0">
+        <v>27.870000000000001</v>
+      </c>
+      <c r="M10" s="0">
+        <v>0.059999999999999998</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="0">
+        <v>2064492060</v>
+      </c>
+      <c r="C11" s="0">
+        <v>2524094167</v>
+      </c>
+      <c r="D11" s="0">
+        <v>1111936</v>
+      </c>
+      <c r="E11" s="0">
+        <v>225</v>
+      </c>
+      <c r="F11" s="0">
+        <v>2361</v>
+      </c>
+      <c r="G11" s="0">
+        <v>1.04</v>
+      </c>
+      <c r="H11" s="0">
+        <v>9.8900000000000006</v>
+      </c>
+      <c r="I11" s="0">
+        <v>81.790000000000006</v>
+      </c>
+      <c r="J11" s="0">
+        <v>4747</v>
+      </c>
+      <c r="K11" s="0">
+        <v>6445.6000000000004</v>
+      </c>
+      <c r="L11" s="0">
+        <v>28.620000000000001</v>
+      </c>
+      <c r="M11" s="0">
+        <v>0.057000000000000002</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="0">
+        <v>18729620110</v>
+      </c>
+      <c r="C12" s="0">
+        <v>22743184682</v>
+      </c>
+      <c r="D12" s="0">
+        <v>1313117</v>
+      </c>
+      <c r="E12" s="0">
+        <v>247</v>
+      </c>
+      <c r="F12" s="0">
+        <v>19193</v>
+      </c>
+      <c r="G12" s="0">
+        <v>1.1100000000000001</v>
+      </c>
+      <c r="H12" s="0">
+        <v>10.74</v>
+      </c>
+      <c r="I12" s="0">
+        <v>82.349999999999994</v>
+      </c>
+      <c r="J12" s="0">
+        <v>4806</v>
+      </c>
+      <c r="K12" s="0">
+        <v>8611.1700000000001</v>
+      </c>
+      <c r="L12" s="0">
+        <v>34.920000000000002</v>
+      </c>
+      <c r="M12" s="0">
+        <v>0.070000000000000007</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="0">
+        <v>9876672620</v>
+      </c>
+      <c r="C13" s="0">
+        <v>12463211572</v>
+      </c>
+      <c r="D13" s="0">
+        <v>1941310</v>
+      </c>
+      <c r="E13" s="0">
+        <v>310</v>
+      </c>
+      <c r="F13" s="0">
+        <v>8624</v>
+      </c>
+      <c r="G13" s="0">
+        <v>1.3400000000000001</v>
+      </c>
+      <c r="H13" s="0">
+        <v>12.640000000000001</v>
+      </c>
+      <c r="I13" s="0">
+        <v>79.25</v>
+      </c>
+      <c r="J13" s="0">
+        <v>4664</v>
+      </c>
+      <c r="K13" s="0">
+        <v>10326.940000000001</v>
+      </c>
+      <c r="L13" s="0">
+        <v>33.32</v>
+      </c>
+      <c r="M13" s="0">
+        <v>0.067000000000000004</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="0">
+        <v>152565256475</v>
+      </c>
+      <c r="C14" s="0">
+        <v>183096112728</v>
+      </c>
+      <c r="D14" s="0">
+        <v>734883</v>
+      </c>
+      <c r="E14" s="0">
+        <v>164</v>
+      </c>
+      <c r="F14" s="0">
+        <v>729570</v>
+      </c>
+      <c r="G14" s="0">
+        <v>2.9300000000000002</v>
+      </c>
+      <c r="H14" s="0">
+        <v>10.08</v>
+      </c>
+      <c r="I14" s="0">
+        <v>83.329999999999998</v>
+      </c>
+      <c r="J14" s="0">
+        <v>1391</v>
+      </c>
+      <c r="K14" s="0">
+        <v>4645.3900000000003</v>
+      </c>
+      <c r="L14" s="0">
+        <v>26.350000000000001</v>
+      </c>
+      <c r="M14" s="0">
+        <v>0.064000000000000001</v>
       </c>
     </row>
   </sheetData>
